--- a/DataTables/Datas/slotstate.xlsx
+++ b/DataTables/Datas/slotstate.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="slotstate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="slotstate" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:DQ19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -653,6 +653,381 @@
           <t>dengmie</t>
         </is>
       </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>wxr2_ying</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>wxr2_tui2</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>wxr2_tui1</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>wxr2_bozi</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>wxr2_st</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>wxr2_shou2</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>wxr2_shou1</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>wxr2_tou</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>wxr2_yan2</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>wxr2_yan1</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>wxr2_zui</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>wxr2_shou3</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>ying</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>shou_r2</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>tui_r</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>tui_l</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>tui_l2</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>shou_r</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>shou_l</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>tou</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>bq1</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>xing2</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>xing</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>tx1</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>tou3</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>tou7</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>tou4</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>tou5</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>tou6</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>tou8</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>shou4</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>jiao</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>shou2</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>shou1</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>guang</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>rtui</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>ltui</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>kua</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>rxiaobi</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>rdabi</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>rquan</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>lxiaobi</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>lquan</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>ldabi</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fa</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>rsdhou1</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>lshou1</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>shenti</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>yaodai</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>bq</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>后臂</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>右臂</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>左臂</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>右腿</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>左腿</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>裆部</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>头大</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>脸大</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>头小</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>脸小</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>绑带</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>胳膊</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>肩带</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -885,6 +1260,381 @@
           <t>int</t>
         </is>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1122,6 +1872,381 @@
       <c r="AT4" t="inlineStr">
         <is>
           <t>dengmie插槽</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>wxr2_ying插槽</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>wxr2_tui2插槽</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>wxr2_tui1插槽</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>wxr2_bozi插槽</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>wxr2_st插槽</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>wxr2_shou2插槽</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>wxr2_shou1插槽</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>wxr2_tou插槽</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>wxr2_yan2插槽</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>wxr2_yan1插槽</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>wxr2_zui插槽</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>wxr2_shou3插槽</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>ying插槽</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>shou_r2插槽</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>tui_r插槽</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>st插槽</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>tui_l插槽</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>tui_l2插槽</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>shou_r插槽</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>shou_l插槽</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>tou插槽</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>bq1插槽</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>xing2插槽</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>xing插槽</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>dead插槽</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>tx1插槽</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>tou3插槽</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>tou7插槽</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>tou4插槽</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>tou5插槽</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>tou6插槽</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>tou8插槽</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>shou4插槽</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>jiao插槽</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>shou2插槽</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>3_3插槽</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>3_2插槽</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>3_1插槽</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>2_3插槽</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>2_2插槽</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>shou1插槽</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>2_1插槽</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>1_4插槽</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>1_3插槽</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>1_2插槽</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>1_1插槽</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>guang插槽</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>rtui插槽</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>ltui插槽</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>kua插槽</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>rxiaobi插槽</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>rdabi插槽</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>rquan插槽</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>lxiaobi插槽</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>lquan插槽</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>ldabi插槽</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>fa插槽</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>rsdhou1插槽</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>lshou1插槽</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>shenti插槽</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>yaodai插槽</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>bq插槽</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>后臂插槽</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>右臂插槽</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>左臂插槽</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>右腿插槽</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>左腿插槽</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>裆部插槽</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>头大插槽</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>脸大插槽</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>头小插槽</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>脸小插槽</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>绑带插槽</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>胳膊插槽</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>肩带插槽</t>
         </is>
       </c>
     </row>
@@ -1524,6 +2649,57 @@
       <c r="AO9" t="n">
         <v>0</v>
       </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -1659,6 +2835,2355 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C19" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ19" t="n">
         <v>0</v>
       </c>
     </row>
